--- a/data/trans_camb/P34A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -3,45</t>
+          <t>-19,73; -3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 5,09</t>
+          <t>-12,55; 4,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 16,11</t>
+          <t>-3,38; 14,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 10,3</t>
+          <t>-6,23; 11,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 15,47</t>
+          <t>-0,02; 15,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 24,64</t>
+          <t>9,27; 23,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 0,66</t>
+          <t>-10,64; 0,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 7,62</t>
+          <t>-3,85; 8,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 17,47</t>
+          <t>5,47; 17,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,09; -9,72</t>
+          <t>-49,85; -11,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 15,9</t>
+          <t>-30,75; 13,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 51,59</t>
+          <t>-8,36; 45,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 35,28</t>
+          <t>-16,13; 37,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 53,27</t>
+          <t>-0,02; 57,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,13; 85,39</t>
+          <t>23,84; 82,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 2,18</t>
+          <t>-28,05; 1,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 24,43</t>
+          <t>-10,24; 23,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,88; 54,71</t>
+          <t>14,34; 54,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,1; -5,92</t>
+          <t>-17,07; -4,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 2,49</t>
+          <t>-9,48; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 13,56</t>
+          <t>-2,05; 11,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -1,44</t>
+          <t>-13,71; -1,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,64; -0,12</t>
+          <t>-12,26; -0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 15,25</t>
+          <t>3,67; 15,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -4,64</t>
+          <t>-14,01; -5,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -0,32</t>
+          <t>-8,94; -0,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 11,92</t>
+          <t>2,42; 11,96</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,49; -18,98</t>
+          <t>-47,63; -16,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 8,36</t>
+          <t>-26,13; 11,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 44,79</t>
+          <t>-5,79; 37,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -3,52</t>
+          <t>-29,83; -3,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,82; -0,19</t>
+          <t>-26,86; -1,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 37,79</t>
+          <t>7,98; 38,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,69; -12,85</t>
+          <t>-35,28; -14,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,5; -0,96</t>
+          <t>-22,12; -0,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 33,87</t>
+          <t>6,27; 33,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,13; -14,86</t>
+          <t>-29,77; -15,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,11; -2,58</t>
+          <t>-17,37; -2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 3,85</t>
+          <t>-12,45; 2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,27; -14,4</t>
+          <t>-28,18; -15,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 4,32</t>
+          <t>-11,05; 4,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 5,83</t>
+          <t>-8,38; 5,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,42; -17,54</t>
+          <t>-27,11; -17,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -1,65</t>
+          <t>-11,71; -1,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 2,03</t>
+          <t>-7,64; 2,37</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,23; -40,52</t>
+          <t>-66,15; -41,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,35; -6,95</t>
+          <t>-39,76; -7,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 10,01</t>
+          <t>-27,47; 5,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,57; -39,13</t>
+          <t>-63,31; -38,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 11,76</t>
+          <t>-24,75; 11,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 16,25</t>
+          <t>-18,48; 14,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-62,84; -45,26</t>
+          <t>-61,43; -44,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,0; -4,07</t>
+          <t>-26,53; -3,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 5,43</t>
+          <t>-17,43; 6,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,87; -3,92</t>
+          <t>-17,97; -4,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,92; -9,88</t>
+          <t>-23,09; -10,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 5,56</t>
+          <t>-12,09; 6,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -1,15</t>
+          <t>-14,84; -1,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 0,11</t>
+          <t>-13,68; 0,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 8,68</t>
+          <t>-19,33; 8,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -5,05</t>
+          <t>-14,48; -4,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -6,82</t>
+          <t>-17,36; -6,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 5,87</t>
+          <t>-13,47; 5,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,15; -11,31</t>
+          <t>-42,02; -12,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,96; -28,36</t>
+          <t>-55,84; -29,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 15,53</t>
+          <t>-29,47; 17,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,08; -2,85</t>
+          <t>-33,02; -3,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,65; 0,05</t>
+          <t>-30,09; 1,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 21,05</t>
+          <t>-44,53; 21,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,59; -13,18</t>
+          <t>-33,63; -11,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -17,66</t>
+          <t>-40,51; -18,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 15,04</t>
+          <t>-32,38; 12,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-30,32; -11,34</t>
+          <t>-30,97; -11,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,32; -5,57</t>
+          <t>-24,54; -5,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-48,21; -31,7</t>
+          <t>-47,66; -31,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -20,19</t>
+          <t>-39,35; -20,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,67; -10,12</t>
+          <t>-29,33; -10,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-61,71; -47,1</t>
+          <t>-61,49; -47,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-32,86; -19,34</t>
+          <t>-32,55; -18,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-23,73; -10,5</t>
+          <t>-23,9; -10,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-52,33; -41,09</t>
+          <t>-52,36; -41,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,1; -25,28</t>
+          <t>-57,26; -26,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,58; -12,64</t>
+          <t>-44,93; -11,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,42; -70,27</t>
+          <t>-86,71; -71,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,71; -31,51</t>
+          <t>-55,34; -32,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,24; -16,52</t>
+          <t>-40,78; -15,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,86; -73,96</t>
+          <t>-84,14; -74,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-52,68; -34,14</t>
+          <t>-52,6; -34,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,13; -18,95</t>
+          <t>-38,29; -19,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,63; -74,94</t>
+          <t>-83,5; -74,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-30,51; -16,08</t>
+          <t>-31,04; -15,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 5,06</t>
+          <t>-10,94; 5,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 10,32</t>
+          <t>-5,28; 10,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-33,39; -17,63</t>
+          <t>-33,15; -17,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 5,14</t>
+          <t>-12,25; 4,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 4,61</t>
+          <t>-9,83; 5,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-29,52; -19,39</t>
+          <t>-30,22; -19,53</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 2,78</t>
+          <t>-9,75; 2,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 5,35</t>
+          <t>-5,33; 5,59</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,08; -46,98</t>
+          <t>-73,54; -46,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 14,66</t>
+          <t>-26,48; 15,16</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 30,18</t>
+          <t>-12,87; 31,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-68,43; -43,36</t>
+          <t>-67,95; -42,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 12,8</t>
+          <t>-25,22; 10,78</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 11,76</t>
+          <t>-20,31; 13,94</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-67,35; -50,06</t>
+          <t>-67,94; -50,42</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 7,1</t>
+          <t>-21,69; 6,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 14,11</t>
+          <t>-12,08; 14,64</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-29,56; -18,74</t>
+          <t>-29,13; -18,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 1,17</t>
+          <t>-10,21; 0,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,75; -10,32</t>
+          <t>-22,42; -11,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-25,62; -14,97</t>
+          <t>-26,02; -15,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,81</t>
+          <t>-5,32; 5,88</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -3,91</t>
+          <t>-33,91; -3,85</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-26,05; -18,7</t>
+          <t>-25,84; -18,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 1,52</t>
+          <t>-6,1; 1,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-27,64; -9,42</t>
+          <t>-30,6; -9,55</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -45,02</t>
+          <t>-61,76; -44,22</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 2,69</t>
+          <t>-21,6; 1,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,34; -24,61</t>
+          <t>-47,34; -25,83</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,35; -34,39</t>
+          <t>-52,79; -35,32</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 13,64</t>
+          <t>-10,94; 13,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,61; -8,28</t>
+          <t>-67,01; -8,29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-54,94; -42,38</t>
+          <t>-54,33; -42,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 3,51</t>
+          <t>-12,86; 3,86</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-59,29; -20,96</t>
+          <t>-63,01; -21,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -16,29</t>
+          <t>-25,74; -16,32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -1,84</t>
+          <t>-11,83; -1,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-37,93; -12,13</t>
+          <t>-36,15; -12,97</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-19,77; -9,58</t>
+          <t>-19,77; -9,85</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 1,97</t>
+          <t>-7,97; 2,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-20,79; -11,33</t>
+          <t>-20,36; -10,88</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -14,36</t>
+          <t>-21,21; -14,47</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -1,03</t>
+          <t>-8,55; -1,46</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-32,21; -14,06</t>
+          <t>-31,33; -13,65</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,99; -37,55</t>
+          <t>-53,88; -37,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-25,57; -4,38</t>
+          <t>-24,99; -3,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-78,23; -27,68</t>
+          <t>-76,43; -28,74</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,6; -19,71</t>
+          <t>-36,52; -19,69</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 4,02</t>
+          <t>-14,68; 4,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-38,71; -23,31</t>
+          <t>-37,78; -21,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-42,78; -31,01</t>
+          <t>-42,47; -30,77</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,36; -2,17</t>
+          <t>-16,89; -3,12</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-65,14; -29,32</t>
+          <t>-64,05; -28,67</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -16,22</t>
+          <t>-20,83; -16,49</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -4,69</t>
+          <t>-9,75; -4,63</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -6,9</t>
+          <t>-16,72; -6,86</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -12,67</t>
+          <t>-17,48; -12,8</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -1,31</t>
+          <t>-5,77; -0,92</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-15,27; -4,63</t>
+          <t>-16,25; -4,61</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -15,23</t>
+          <t>-18,44; -15,26</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -3,61</t>
+          <t>-6,95; -3,56</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -6,28</t>
+          <t>-13,38; -6,49</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -40,56</t>
+          <t>-49,52; -41,25</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -11,68</t>
+          <t>-22,99; -11,44</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -16,96</t>
+          <t>-40,87; -17,1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-36,76; -28,18</t>
+          <t>-36,99; -28,46</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-12,5; -2,98</t>
+          <t>-12,33; -2,07</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -10,28</t>
+          <t>-34,22; -10,1</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-41,64; -35,53</t>
+          <t>-41,52; -35,45</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -8,55</t>
+          <t>-15,55; -8,29</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-31,22; -14,41</t>
+          <t>-30,65; -14,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P34A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P34A_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,64</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>13,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,73; -3,7</t>
+          <t>-19,62; -3,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 4,11</t>
+          <t>-12,21; 4,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 14,38</t>
+          <t>-0,06; 16,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 11,05</t>
+          <t>-5,19; 11,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 15,89</t>
+          <t>-0,68; 16,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 23,7</t>
+          <t>9,78; 25,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 0,53</t>
+          <t>-10,8; 0,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 8,02</t>
+          <t>-4,06; 7,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 17,27</t>
+          <t>7,79; 19,42</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,85; -11,37</t>
+          <t>-48,27; -9,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 13,31</t>
+          <t>-31,03; 12,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 45,08</t>
+          <t>0,88; 53,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 37,7</t>
+          <t>-13,82; 38,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 57,45</t>
+          <t>-1,95; 57,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,84; 82,43</t>
+          <t>24,72; 86,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 1,63</t>
+          <t>-27,54; 3,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 23,91</t>
+          <t>-10,78; 22,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 54,52</t>
+          <t>20,2; 62,27</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>8,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -4,96</t>
+          <t>-16,51; -5,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 3,2</t>
+          <t>-9,16; 2,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 11,57</t>
+          <t>-0,41; 13,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -1,59</t>
+          <t>-13,92; -1,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -0,76</t>
+          <t>-12,3; 0,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 15,36</t>
+          <t>3,88; 15,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -5,15</t>
+          <t>-14,15; -5,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -0,23</t>
+          <t>-8,91; -0,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 11,96</t>
+          <t>3,63; 12,76</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,63; -16,8</t>
+          <t>-46,9; -19,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 11,15</t>
+          <t>-25,43; 8,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 37,58</t>
+          <t>-1,33; 43,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,83; -3,94</t>
+          <t>-29,95; -3,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,86; -1,96</t>
+          <t>-26,59; 1,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 38,57</t>
+          <t>8,07; 37,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -14,6</t>
+          <t>-34,61; -15,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,12; -0,35</t>
+          <t>-21,98; -1,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 33,44</t>
+          <t>8,68; 35,15</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-4,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-2,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,77; -15,35</t>
+          <t>-30,26; -16,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -2,74</t>
+          <t>-17,39; -2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 2,02</t>
+          <t>-12,18; 2,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,18; -15,16</t>
+          <t>-27,61; -14,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 4,31</t>
+          <t>-11,48; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 5,53</t>
+          <t>-6,92; 5,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,11; -17,13</t>
+          <t>-26,88; -17,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,71; -1,41</t>
+          <t>-12,18; -1,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,37</t>
+          <t>-7,52; 2,63</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,11%</t>
+          <t>-11,22%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,32%</t>
+          <t>-1,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,09%</t>
+          <t>-5,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,15; -41,19</t>
+          <t>-65,9; -42,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,76; -7,66</t>
+          <t>-37,98; -5,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 5,52</t>
+          <t>-26,73; 8,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,31; -38,86</t>
+          <t>-63,37; -37,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 11,86</t>
+          <t>-25,84; 9,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 14,63</t>
+          <t>-15,76; 16,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,43; -44,27</t>
+          <t>-61,82; -44,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,53; -3,5</t>
+          <t>-27,01; -3,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 6,32</t>
+          <t>-17,32; 7,01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-4,2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,34</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-3,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,97; -4,47</t>
+          <t>-17,73; -3,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,09; -10,34</t>
+          <t>-23,62; -9,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 6,01</t>
+          <t>-13,12; 3,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -1,22</t>
+          <t>-14,67; -0,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 0,43</t>
+          <t>-13,86; 0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 8,92</t>
+          <t>-9,51; 3,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -4,64</t>
+          <t>-14,45; -4,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -6,72</t>
+          <t>-16,75; -6,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 5,03</t>
+          <t>-8,55; 2,22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,34%</t>
+          <t>-10,88%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,38%</t>
+          <t>-7,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,68%</t>
+          <t>-8,61%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,02; -12,38</t>
+          <t>-42,34; -9,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,84; -29,65</t>
+          <t>-56,83; -28,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 17,53</t>
+          <t>-32,39; 10,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,02; -3,1</t>
+          <t>-33,39; -2,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 1,17</t>
+          <t>-30,79; 1,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,53; 21,05</t>
+          <t>-21,15; 10,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,63; -11,92</t>
+          <t>-33,95; -12,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,51; -18,07</t>
+          <t>-39,22; -17,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 12,74</t>
+          <t>-20,44; 5,84</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-39,92</t>
+          <t>-40,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-54,32</t>
+          <t>-54,37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-47,11</t>
+          <t>-47,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-30,97; -11,68</t>
+          <t>-30,68; -11,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,54; -5,36</t>
+          <t>-23,52; -4,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-47,66; -31,55</t>
+          <t>-49,08; -32,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-39,35; -20,47</t>
+          <t>-39,42; -19,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,33; -10,05</t>
+          <t>-28,58; -9,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-61,49; -47,01</t>
+          <t>-61,51; -47,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -18,86</t>
+          <t>-32,65; -19,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-23,9; -10,79</t>
+          <t>-24,51; -11,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-52,36; -41,22</t>
+          <t>-52,89; -41,82</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-80,21%</t>
+          <t>-81,57%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-79,86%</t>
+          <t>-79,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-79,81%</t>
+          <t>-80,49%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,26; -26,24</t>
+          <t>-56,83; -25,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,93; -11,25</t>
+          <t>-43,63; -10,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,71; -71,03</t>
+          <t>-87,31; -72,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-55,34; -32,16</t>
+          <t>-55,07; -31,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -15,47</t>
+          <t>-40,28; -15,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,14; -74,02</t>
+          <t>-84,85; -74,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-52,6; -34,51</t>
+          <t>-52,38; -33,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,29; -19,41</t>
+          <t>-38,88; -19,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,5; -74,7</t>
+          <t>-84,3; -75,9</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-2,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>1,12</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-31,04; -15,66</t>
+          <t>-31,37; -16,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 5,04</t>
+          <t>-11,61; 5,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 10,5</t>
+          <t>-3,13; 12,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-33,15; -17,87</t>
+          <t>-33,21; -18,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 4,07</t>
+          <t>-11,53; 4,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 5,54</t>
+          <t>-10,17; 5,46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -19,53</t>
+          <t>-30,19; -19,5</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 2,65</t>
+          <t>-9,2; 2,5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 5,59</t>
+          <t>-4,88; 6,43</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-5,92%</t>
+          <t>-4,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,29%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,54; -46,21</t>
+          <t>-73,34; -48,74</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 15,16</t>
+          <t>-27,54; 15,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 31,78</t>
+          <t>-7,26; 37,37</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-67,95; -42,71</t>
+          <t>-67,57; -44,09</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 10,78</t>
+          <t>-23,18; 12,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 13,94</t>
+          <t>-20,98; 12,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-67,94; -50,42</t>
+          <t>-67,72; -50,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 6,78</t>
+          <t>-20,94; 6,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 14,64</t>
+          <t>-10,89; 17,04</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-16,6</t>
+          <t>-15,72</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-15,3</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-15,75</t>
+          <t>-10,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-29,13; -18,57</t>
+          <t>-29,02; -18,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 0,73</t>
+          <t>-10,31; 1,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,42; -11,17</t>
+          <t>-21,27; -10,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-26,02; -15,35</t>
+          <t>-26,21; -15,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 5,88</t>
+          <t>-5,62; 5,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-33,91; -3,85</t>
+          <t>-10,72; 0,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -18,16</t>
+          <t>-26,01; -18,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,68</t>
+          <t>-6,4; 1,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-30,6; -9,55</t>
+          <t>-14,12; -5,92</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-37,07%</t>
+          <t>-35,12%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-33,09%</t>
+          <t>-11,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-34,6%</t>
+          <t>-22,48%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-61,76; -44,22</t>
+          <t>-61,53; -44,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 1,63</t>
+          <t>-22,04; 1,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,34; -25,83</t>
+          <t>-45,71; -24,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,79; -35,32</t>
+          <t>-52,84; -34,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 13,82</t>
+          <t>-11,43; 12,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-67,01; -8,29</t>
+          <t>-21,53; 0,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-54,33; -42,04</t>
+          <t>-54,99; -42,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 3,86</t>
+          <t>-13,5; 4,02</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-63,01; -21,39</t>
+          <t>-29,78; -13,64</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-22,25</t>
+          <t>-14,96</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-15,89</t>
+          <t>-16,3</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-19,95</t>
+          <t>-15,63</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-25,74; -16,32</t>
+          <t>-26,01; -16,12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,83; -1,23</t>
+          <t>-12,48; -2,27</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-36,15; -12,97</t>
+          <t>-19,81; -10,11</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-19,77; -9,85</t>
+          <t>-20,03; -9,99</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 2,21</t>
+          <t>-8,4; 2,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -10,88</t>
+          <t>-21,71; -11,89</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-21,21; -14,47</t>
+          <t>-21,28; -14,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -1,46</t>
+          <t>-8,86; -1,42</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-31,33; -13,65</t>
+          <t>-19,33; -12,3</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-49,17%</t>
+          <t>-33,07%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-30,79%</t>
+          <t>-31,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-41,14%</t>
+          <t>-32,25%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-53,88; -37,51</t>
+          <t>-54,52; -37,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,99; -3,23</t>
+          <t>-25,54; -5,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-76,43; -28,74</t>
+          <t>-41,24; -23,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,52; -19,69</t>
+          <t>-37,13; -20,13</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 4,5</t>
+          <t>-15,36; 4,3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,78; -21,91</t>
+          <t>-39,45; -23,86</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -30,77</t>
+          <t>-42,54; -30,59</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,89; -3,12</t>
+          <t>-17,45; -3,04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-64,05; -28,67</t>
+          <t>-38,31; -26,5</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-7,62</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-5,64</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-9,1</t>
+          <t>-6,56</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -16,49</t>
+          <t>-20,84; -16,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -4,63</t>
+          <t>-9,63; -4,87</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -6,86</t>
+          <t>-10,28; -5,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -12,8</t>
+          <t>-17,47; -12,86</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -0,92</t>
+          <t>-5,72; -0,72</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -4,61</t>
+          <t>-7,93; -3,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -15,26</t>
+          <t>-18,42; -15,26</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -3,56</t>
+          <t>-7,07; -3,6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -6,49</t>
+          <t>-8,16; -4,88</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-24,77%</t>
+          <t>-18,55%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-17,7%</t>
+          <t>-12,22%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-20,86%</t>
+          <t>-15,04%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-49,52; -41,25</t>
+          <t>-49,31; -40,96</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-22,99; -11,44</t>
+          <t>-22,76; -12,18</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-40,87; -17,1</t>
+          <t>-24,19; -12,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-36,99; -28,46</t>
+          <t>-37,11; -28,88</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -2,07</t>
+          <t>-12,07; -1,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -10,1</t>
+          <t>-16,65; -7,64</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-41,52; -35,45</t>
+          <t>-41,4; -35,65</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -8,29</t>
+          <t>-15,82; -8,36</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -14,9</t>
+          <t>-18,36; -11,49</t>
         </is>
       </c>
     </row>
